--- a/Python/big-pitch/output/02_model_note_single_factor_gam_v3.xlsx
+++ b/Python/big-pitch/output/02_model_note_single_factor_gam_v3.xlsx
@@ -497,34 +497,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
-        <v>258180.3387423157</v>
+        <v>258689.1932836018</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46049.90212640492</v>
+        <v>46052.00690258334</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46049.90666536232</v>
+        <v>46052.00854773285</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.004538957395833333</v>
+        <v>0.001645149513888889</v>
       </c>
       <c r="F2" t="n">
-        <v>43.00951104228083</v>
+        <v>130.1640289447675</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1438122806913</v>
+        <v>6.134113661332731</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -537,34 +537,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>258181.0763026692</v>
+        <v>258689.392882738</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46049.86693450206</v>
+        <v>46051.99883025452</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46049.86997116915</v>
+        <v>46052.00059235536</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.003036667094907408</v>
+        <v>0.001762100833333333</v>
       </c>
       <c r="F3" t="n">
-        <v>58.66714435630819</v>
+        <v>175.4799653401012</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.625596218434346</v>
+        <v>3.893011444406327</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -580,31 +580,31 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>258181.2665573194</v>
+        <v>258689.5463611671</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46049.87274355508</v>
+        <v>46051.99584973062</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46049.87593930868</v>
+        <v>46051.99745599308</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.003195753599537037</v>
+        <v>0.001606262453703704</v>
       </c>
       <c r="F4" t="n">
-        <v>59.39180465040852</v>
+        <v>195.0729490973071</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.998918200132162</v>
+        <v>6.96349414686332</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -617,34 +617,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
-        <v>258181.8701479139</v>
+        <v>258690.6159939488</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46049.89519834105</v>
+        <v>46052.00528195581</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46049.89840437746</v>
+        <v>46052.00690258334</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.003206036412037037</v>
+        <v>0.001620627523148148</v>
       </c>
       <c r="F5" t="n">
-        <v>316.7784897383743</v>
+        <v>114.9812493215996</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.160910929211114</v>
+        <v>18.96189620849591</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
@@ -657,34 +657,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258184.4816537273</v>
+        <v>258693.6480036801</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46049.89021430359</v>
+        <v>46051.97677406036</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46049.89295215438</v>
+        <v>46051.97845706996</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.002737850798611111</v>
+        <v>0.001683009594907407</v>
       </c>
       <c r="F6" t="n">
-        <v>102.8045740004001</v>
+        <v>79.46826267845638</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>9.107644210742254</v>
+        <v>30.96922836800023</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
@@ -700,31 +700,31 @@
         <v>21</v>
       </c>
       <c r="B7" t="n">
-        <v>258190.9638642929</v>
+        <v>258694.922718443</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46049.88520735422</v>
+        <v>46052.0036552569</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46049.88781562117</v>
+        <v>46052.00528195581</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.002608266944444444</v>
+        <v>0.001626698912037037</v>
       </c>
       <c r="F7" t="n">
-        <v>23.437728553244</v>
+        <v>89.3118617509935</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>18.44422259826253</v>
+        <v>35.00396186541898</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
         <v>4</v>
@@ -737,34 +737,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B8" t="n">
-        <v>258191.3631657392</v>
+        <v>258695.866571492</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46049.87819774991</v>
+        <v>46052.01213402562</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46049.88084095003</v>
+        <v>46052.01393223496</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.002643200127314815</v>
+        <v>0.001798209351851852</v>
       </c>
       <c r="F8" t="n">
-        <v>17.89298705940434</v>
+        <v>672.7020172541562</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>18.96645769253936</v>
+        <v>2.719124103961089</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
@@ -777,34 +777,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>258192.5329639195</v>
+        <v>258697.1235683725</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46049.85668981554</v>
+        <v>46051.98978468169</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46049.86041552131</v>
+        <v>46051.99177873067</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.003725705763888889</v>
+        <v>0.001994048981481482</v>
       </c>
       <c r="F9" t="n">
-        <v>897.0505998710386</v>
+        <v>1.044150940859716</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.10239539755582</v>
+        <v>1.038975555498986</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -817,34 +817,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>258192.8507199855</v>
+        <v>258697.2083770021</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46049.85306118082</v>
+        <v>46051.98783269082</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46049.85668979617</v>
+        <v>46051.98978468169</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.003628615347222222</v>
+        <v>0.001951990868055555</v>
       </c>
       <c r="F10" t="n">
-        <v>911.5241502210832</v>
+        <v>1.101706596468368</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.271524074606178</v>
+        <v>1.110443085697477</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -857,34 +857,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>258220.8021956005</v>
+        <v>258697.4170006715</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46049.88781562117</v>
+        <v>46051.98586683535</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>46049.89021430359</v>
+        <v>46051.98783269082</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.002398682418981482</v>
+        <v>0.001965855474537037</v>
       </c>
       <c r="F11" t="n">
-        <v>29.68666465476786</v>
+        <v>1.239602647605565</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>56.32316125849356</v>
+        <v>1.309486865058522</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
@@ -897,34 +897,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>258223.8422484106</v>
+        <v>258698.4701764627</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46049.89840443843</v>
+        <v>46051.99269935226</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>46049.90212635139</v>
+        <v>46051.99463954111</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.003721912962962963</v>
+        <v>0.001940188854166667</v>
       </c>
       <c r="F12" t="n">
-        <v>300.7544717553489</v>
+        <v>58.33239802991491</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.33830931945197</v>
+        <v>3.554705696688752</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -937,34 +937,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B13" t="n">
-        <v>258225.8599844816</v>
+        <v>258699.6229497225</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46049.86997119235</v>
+        <v>46052.01020872539</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>46049.87274355508</v>
+        <v>46052.012134014</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.002772362731481481</v>
+        <v>0.001925288611111111</v>
       </c>
       <c r="F13" t="n">
-        <v>8.929211114805121</v>
+        <v>259.2799993166492</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>4.091618440968045</v>
+        <v>5.863693020700011</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
@@ -977,34 +977,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B14" t="n">
-        <v>258226.115389741</v>
+        <v>258735.3585611084</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46049.87593930868</v>
+        <v>46052.01550378137</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46049.87819774133</v>
+        <v>46052.22828714402</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.002258432650462963</v>
+        <v>0.2127833626504629</v>
       </c>
       <c r="F14" t="n">
-        <v>48.49045225861254</v>
+        <v>21.59223331149849</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.213078920683926</v>
+        <v>5.62573804768759</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
@@ -1017,34 +1017,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B15" t="n">
+        <v>258735.3593749072</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46052.00854773285</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>46052.01020872539</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.001660992546296296</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33.4375298733002</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.716115723900653</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
         <v>12</v>
-      </c>
-      <c r="B15" t="n">
-        <v>258227.3100938554</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>46049.86041552131</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>46049.86366684445</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.003251323136574074</v>
-      </c>
-      <c r="F15" t="n">
-        <v>678.5637759631717</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.229273312432499</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>11</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
@@ -1057,34 +1057,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>258232.2310348863</v>
+        <v>258735.4916149575</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46049.88084095003</v>
+        <v>46051.97528076165</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46049.88310699551</v>
+        <v>46051.97677386548</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.002266045474537037</v>
+        <v>0.001493103842592593</v>
       </c>
       <c r="F16" t="n">
-        <v>4.322744297822777</v>
+        <v>4.110775936914326</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>8.528987340825262</v>
+        <v>11.45784496379341</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
@@ -1097,34 +1097,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>258233.5049305693</v>
+        <v>258737.6831813468</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46049.89295215438</v>
+        <v>46052.00194339515</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46049.89519820388</v>
+        <v>46052.0036552569</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.002246049490740741</v>
+        <v>0.001711861747685185</v>
       </c>
       <c r="F17" t="n">
-        <v>109.3176936347127</v>
+        <v>328.9057571076111</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>9.535127539540598</v>
+        <v>2.857899554249848</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
@@ -1137,34 +1137,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B18" t="n">
-        <v>258234.391238116</v>
+        <v>258739.4696087316</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46049.86366686146</v>
+        <v>46051.98000395422</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46049.86693447906</v>
+        <v>46051.98165679038</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.003267617604166667</v>
+        <v>0.001652836157407408</v>
       </c>
       <c r="F18" t="n">
-        <v>965.6638309552422</v>
+        <v>10.53513370757097</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1.194521611693438</v>
+        <v>28.50568521492582</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -1177,34 +1177,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B19" t="n">
-        <v>258269.0790010031</v>
+        <v>258739.552547995</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46049.83754142671</v>
+        <v>46052.01393234637</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>46049.84112081747</v>
+        <v>46052.01550378137</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.003579390752314815</v>
+        <v>0.001571435</v>
       </c>
       <c r="F19" t="n">
-        <v>171.4044388492533</v>
+        <v>44.82127431515784</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>124.5311518512259</v>
+        <v>1.899714685541744</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
@@ -1217,34 +1217,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B20" t="n">
-        <v>258274.1455829663</v>
+        <v>258747.4674253823</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46049.88310699551</v>
+        <v>46051.98448574694</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>46049.88520735422</v>
+        <v>46051.98586683535</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.002100358715277778</v>
+        <v>0.001381088414351852</v>
       </c>
       <c r="F20" t="n">
-        <v>77.72878750636917</v>
+        <v>579.3585102320386</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.942795929300807</v>
+        <v>9.899261474089263</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
@@ -1257,34 +1257,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>258286.6972163014</v>
+        <v>258756.7245805842</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46049.90666536232</v>
+        <v>46051.99745599308</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46049.91010081633</v>
+        <v>46051.99883025452</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.003435454016203703</v>
+        <v>0.001374261446759259</v>
       </c>
       <c r="F21" t="n">
-        <v>49.28527971650618</v>
+        <v>969.2575561702855</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>5.481706376091719</v>
+        <v>10.24319712030404</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
         <v>4</v>
@@ -1297,34 +1297,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>258302.2130515705</v>
+        <v>258764.8174290394</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46049.83129876712</v>
+        <v>46051.99463954111</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46049.83416726676</v>
+        <v>46051.99584973062</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.002868499641203704</v>
+        <v>0.001210189513888889</v>
       </c>
       <c r="F22" t="n">
-        <v>1.597524969189335</v>
+        <v>14.31747160138264</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>10.94251827150011</v>
+        <v>63.37885280666345</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -1337,34 +1337,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B23" t="n">
-        <v>258312.4727794146</v>
+        <v>258768.7420952818</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46049.84657998804</v>
+        <v>46051.98293980383</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46049.84900359263</v>
+        <v>46051.98448574694</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.002423604594907407</v>
+        <v>0.001545943101851852</v>
       </c>
       <c r="F23" t="n">
-        <v>149.4044229992054</v>
+        <v>165.2160130295345</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>200.012254306207</v>
+        <v>252.3622204297702</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
@@ -1377,28 +1377,28 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>258440.7022515479</v>
+        <v>258787.5610017047</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46049.84343892257</v>
+        <v>46052.00059235536</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46049.84657980149</v>
+        <v>46052.00194335876</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.003140878923611111</v>
+        <v>0.001351003402777778</v>
       </c>
       <c r="F24" t="n">
-        <v>26.84009512778275</v>
+        <v>225.2141434809289</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>132.3157091175371</v>
+        <v>3.431583156953879</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1420,31 +1420,31 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>258566.3753350695</v>
+        <v>258804.1613441213</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46049.91010087592</v>
+        <v>46052.22828717891</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46049.91299680528</v>
+        <v>46052.22981502196</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.002895929363425926</v>
+        <v>0.001527843055555555</v>
       </c>
       <c r="F25" t="n">
-        <v>11.34372292965733</v>
+        <v>155.2896620832054</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1872628640478</v>
+        <v>18.86572292307279</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
@@ -1460,31 +1460,31 @@
         <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>258620.2753617407</v>
+        <v>258843.6627958062</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46049.84112085211</v>
+        <v>46051.9784571</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>46049.84343892257</v>
+        <v>46051.98000393101</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.002318070462962963</v>
+        <v>0.001546831006944444</v>
       </c>
       <c r="F26" t="n">
-        <v>483.744606185143</v>
+        <v>66.40017753631193</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>4.447315814708903</v>
+        <v>505.0752973650522</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
@@ -1497,34 +1497,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>258694.275225899</v>
+        <v>258892.8729323023</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46049.84900359263</v>
+        <v>46051.97196203412</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>46049.85096421141</v>
+        <v>46051.97374828895</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.001960618784722222</v>
+        <v>0.001786254826388889</v>
       </c>
       <c r="F27" t="n">
-        <v>258.9509327941674</v>
+        <v>12.25218287144648</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>26.63578531175852</v>
+        <v>670.8765666853044</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
@@ -1537,34 +1537,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B28" t="n">
-        <v>258732.2905472642</v>
+        <v>258918.9761555594</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46049.85096421141</v>
+        <v>46051.97374828895</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>46049.85306118082</v>
+        <v>46051.97528076165</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.002096969409722222</v>
+        <v>0.001532472696759259</v>
       </c>
       <c r="F28" t="n">
-        <v>66.96723416904511</v>
+        <v>32.77701570798548</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>53.76652556995594</v>
+        <v>447.8244658247332</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
@@ -1577,34 +1577,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B29" t="n">
-        <v>259013.0124302969</v>
+        <v>259337.1278573925</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46049.83416726676</v>
+        <v>46051.98165679038</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>46049.83754139103</v>
+        <v>46051.98293980383</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.003374124270833333</v>
+        <v>0.001283013449074074</v>
       </c>
       <c r="F29" t="n">
-        <v>2.065010326278164</v>
+        <v>415.7492248467317</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>320.2947007926432</v>
+        <v>648.3738781916479</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
@@ -1617,28 +1617,28 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B30" t="n">
-        <v>259102.8321818608</v>
+        <v>259345.6182053462</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46049.82810871104</v>
+        <v>46051.99177873067</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46049.82955661912</v>
+        <v>46051.99269935226</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.001447908078703704</v>
+        <v>0.0009206215856481481</v>
       </c>
       <c r="F30" t="n">
-        <v>1.422961186461628</v>
+        <v>4.63418601019545</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>221.1100644348938</v>
+        <v>81.43018020851031</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -1657,28 +1657,28 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="n">
-        <v>259176.0590212971</v>
+        <v>259778.723540998</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46049.82955664765</v>
+        <v>46051.97075396999</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46049.83129874485</v>
+        <v>46051.97196202093</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.001742097199074074</v>
+        <v>0.0012080509375</v>
       </c>
       <c r="F31" t="n">
-        <v>10.84728286976355</v>
+        <v>156.1897170657543</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>535.1590439924099</v>
+        <v>701.8513239822224</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>

--- a/Python/big-pitch/output/02_model_note_single_factor_gam_v3.xlsx
+++ b/Python/big-pitch/output/02_model_note_single_factor_gam_v3.xlsx
@@ -497,28 +497,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B2" t="n">
-        <v>258689.1932836018</v>
+        <v>258646.4365396766</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46052.00690258334</v>
+        <v>46052.88863574471</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46052.00854773285</v>
+        <v>46052.8908584172</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.001645149513888889</v>
+        <v>0.002222672488425926</v>
       </c>
       <c r="F2" t="n">
-        <v>130.1640289447675</v>
+        <v>18.3057805107577</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6.134113661332731</v>
+        <v>4.014203313264911</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -537,28 +537,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
-        <v>258689.392882738</v>
+        <v>258646.6014441612</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46051.99883025452</v>
+        <v>46052.87380372969</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46052.00059235536</v>
+        <v>46052.87555169044</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.001762100833333333</v>
+        <v>0.001747960752314815</v>
       </c>
       <c r="F3" t="n">
-        <v>175.4799653401012</v>
+        <v>2.008822327112232</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.893011444406327</v>
+        <v>5.205953730388366</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -577,28 +577,28 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
-        <v>258689.5463611671</v>
+        <v>258646.6101615324</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46051.99584973062</v>
+        <v>46052.87717617552</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46051.99745599308</v>
+        <v>46052.87891720669</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.001606262453703704</v>
+        <v>0.001741031168981481</v>
       </c>
       <c r="F4" t="n">
-        <v>195.0729490973071</v>
+        <v>3.735052106320627</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>6.96349414686332</v>
+        <v>5.261053225282435</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -617,28 +617,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>258690.6159939488</v>
+        <v>258646.6632471957</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46052.00528195581</v>
+        <v>46052.87208619669</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46052.00690258334</v>
+        <v>46052.87380353526</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.001620627523148148</v>
+        <v>0.001717338564814815</v>
       </c>
       <c r="F5" t="n">
-        <v>114.9812493215996</v>
+        <v>2.042093524443632</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>18.96189620849591</v>
+        <v>5.60774447171643</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -657,28 +657,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B6" t="n">
-        <v>258693.6480036801</v>
+        <v>258646.6686495302</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46051.97677406036</v>
+        <v>46052.88075452976</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46051.97845706996</v>
+        <v>46052.88272322084</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.001683009594907407</v>
+        <v>0.001968691087962963</v>
       </c>
       <c r="F6" t="n">
-        <v>79.46826267845638</v>
+        <v>1.751443430834519</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>30.96922836800023</v>
+        <v>5.651435535597294</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -697,28 +697,28 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>258694.922718443</v>
+        <v>258648.9137690699</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46052.0036552569</v>
+        <v>46052.8703826009</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46052.00528195581</v>
+        <v>46052.87208618502</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.001626698912037037</v>
+        <v>0.001703584120370371</v>
       </c>
       <c r="F7" t="n">
-        <v>89.3118617509935</v>
+        <v>2.723458114572092</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>35.00396186541898</v>
+        <v>16.37996700909676</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -737,28 +737,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B8" t="n">
-        <v>258695.866571492</v>
+        <v>258649.0668288959</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46052.01213402562</v>
+        <v>46052.86711198043</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46052.01393223496</v>
+        <v>46052.86881996112</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.001798209351851852</v>
+        <v>0.001707980694444445</v>
       </c>
       <c r="F8" t="n">
-        <v>672.7020172541562</v>
+        <v>1.030159983259402</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.719124103961089</v>
+        <v>16.94969679642261</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -777,34 +777,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>258697.1235683725</v>
+        <v>258649.146169548</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46051.98978468169</v>
+        <v>46052.86370437327</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46051.99177873067</v>
+        <v>46052.8653956108</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.001994048981481482</v>
+        <v>0.001691237534722222</v>
       </c>
       <c r="F9" t="n">
-        <v>1.044150940859716</v>
+        <v>1.125616160122696</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.038975555498986</v>
+        <v>17.24160144411568</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -817,28 +817,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B10" t="n">
-        <v>258697.2083770021</v>
+        <v>258657.2961560398</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46051.98783269082</v>
+        <v>46052.88442916136</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46051.98978468169</v>
+        <v>46052.88691732183</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.001951990868055555</v>
+        <v>0.002488160474537037</v>
       </c>
       <c r="F10" t="n">
-        <v>1.101706596468368</v>
+        <v>5.213862163996157</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.110443085697477</v>
+        <v>2.073353809504978</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -857,34 +857,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>258697.4170006715</v>
+        <v>258657.5902694692</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46051.98586683535</v>
+        <v>46052.8620355332</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>46051.98783269082</v>
+        <v>46052.86370437327</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.001965855474537037</v>
+        <v>0.001668840069444444</v>
       </c>
       <c r="F11" t="n">
-        <v>1.239602647605565</v>
+        <v>1.093760474485375</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1.309486865058522</v>
+        <v>43.55464323313797</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
@@ -897,34 +897,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>258698.4701764627</v>
+        <v>258658.7484107534</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46051.99269935226</v>
+        <v>46052.8653956108</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>46051.99463954111</v>
+        <v>46052.86711198043</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.001940188854166667</v>
+        <v>0.001716369629629629</v>
       </c>
       <c r="F12" t="n">
-        <v>58.33239802991491</v>
+        <v>1.085648988567332</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.554705696688752</v>
+        <v>46.8959085905191</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -937,28 +937,28 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>258699.6229497225</v>
+        <v>258659.4204490422</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46052.01020872539</v>
+        <v>46052.85656460599</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>46052.012134014</v>
+        <v>46052.85838674336</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.001925288611111111</v>
+        <v>0.001822137372685185</v>
       </c>
       <c r="F13" t="n">
-        <v>259.2799993166492</v>
+        <v>81.01518517019791</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>5.863693020700011</v>
+        <v>15.54454852227149</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -977,34 +977,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>258735.3585611084</v>
+        <v>258674.9141210027</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46052.01550378137</v>
+        <v>46052.85471604661</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46052.22828714402</v>
+        <v>46052.85656460599</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.2127833626504629</v>
+        <v>0.001848559375</v>
       </c>
       <c r="F14" t="n">
-        <v>21.59223331149849</v>
+        <v>49.23103953941791</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>5.62573804768759</v>
+        <v>84.96642398135286</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
@@ -1017,34 +1017,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>258735.3593749072</v>
+        <v>258677.1671206705</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46052.00854773285</v>
+        <v>46052.86021632517</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46052.01020872539</v>
+        <v>46052.86203551744</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.001660992546296296</v>
+        <v>0.001819192268518518</v>
       </c>
       <c r="F15" t="n">
-        <v>33.4375298733002</v>
+        <v>49.55465291642794</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>5.716115723900653</v>
+        <v>94.59747271400528</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
@@ -1057,34 +1057,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>258735.4916149575</v>
+        <v>258677.6027919515</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46051.97528076165</v>
+        <v>46052.85838674336</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46051.97677386548</v>
+        <v>46052.86021632517</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.001493103842592593</v>
+        <v>0.00182958181712963</v>
       </c>
       <c r="F16" t="n">
-        <v>4.110775936914326</v>
+        <v>89.46840835450062</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>11.45784496379341</v>
+        <v>96.09947744357601</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
@@ -1097,28 +1097,28 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>258737.6831813468</v>
+        <v>258683.8810782895</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46052.00194339515</v>
+        <v>46052.87891721824</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46052.0036552569</v>
+        <v>46052.88075452976</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.001711861747685185</v>
+        <v>0.001837311516203704</v>
       </c>
       <c r="F17" t="n">
-        <v>328.9057571076111</v>
+        <v>4.791971161745177</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.857899554249848</v>
+        <v>1.223862855470508</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1137,28 +1137,28 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>258739.4696087316</v>
+        <v>258685.3738274496</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46051.98000395422</v>
+        <v>46052.87555171365</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46051.98165679038</v>
+        <v>46052.87717617552</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.001652836157407408</v>
+        <v>0.001624461875</v>
       </c>
       <c r="F18" t="n">
-        <v>10.53513370757097</v>
+        <v>2.234228024571521</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>28.50568521492582</v>
+        <v>5.378293480720544</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1177,34 +1177,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B19" t="n">
-        <v>258739.552547995</v>
+        <v>258685.442825897</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46052.01393234637</v>
+        <v>46052.84899677253</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>46052.01550378137</v>
+        <v>46052.85061080338</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.001571435</v>
+        <v>0.001614030844907408</v>
       </c>
       <c r="F19" t="n">
-        <v>44.82127431515784</v>
+        <v>26.36146161027677</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.899714685541744</v>
+        <v>8.434106312611849</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
@@ -1217,28 +1217,28 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>258747.4674253823</v>
+        <v>258685.9250639592</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46051.98448574694</v>
+        <v>46052.88272323238</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>46051.98586683535</v>
+        <v>46052.88442914978</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.001381088414351852</v>
+        <v>0.001705917395833333</v>
       </c>
       <c r="F20" t="n">
-        <v>579.3585102320386</v>
+        <v>11.40286894142194</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>9.899261474089263</v>
+        <v>3.240564737269163</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1257,34 +1257,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" t="n">
-        <v>258756.7245805842</v>
+        <v>258686.0377306934</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46051.99745599308</v>
+        <v>46052.8688201413</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46051.99883025452</v>
+        <v>46052.8703826009</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.001374261446759259</v>
+        <v>0.001562459606481482</v>
       </c>
       <c r="F21" t="n">
-        <v>969.2575561702855</v>
+        <v>1.570510918265422</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>10.24319712030404</v>
+        <v>13.34631868939419</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
         <v>4</v>
@@ -1297,28 +1297,28 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B22" t="n">
-        <v>258764.8174290394</v>
+        <v>258687.7992082526</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46051.99463954111</v>
+        <v>46052.85061080338</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46051.99584973062</v>
+        <v>46052.85207060938</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.001210189513888889</v>
+        <v>0.00145980599537037</v>
       </c>
       <c r="F22" t="n">
-        <v>14.31747160138264</v>
+        <v>3.926411548440325</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>63.37885280666345</v>
+        <v>4.081611097363391</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1337,34 +1337,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B23" t="n">
-        <v>258768.7420952818</v>
+        <v>258690.267082897</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46051.98293980383</v>
+        <v>46052.8531404137</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46051.98448574694</v>
+        <v>46052.85471604661</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.001545943101851852</v>
+        <v>0.001575632905092592</v>
       </c>
       <c r="F23" t="n">
-        <v>165.2160130295345</v>
+        <v>10.33111304121699</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>252.3622204297702</v>
+        <v>27.75027620291527</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
@@ -1377,34 +1377,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>258787.5610017047</v>
+        <v>258690.7783151804</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46052.00059235536</v>
+        <v>46052.88691734512</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46052.00194335876</v>
+        <v>46052.88863573314</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.001351003402777778</v>
+        <v>0.001718388009259259</v>
       </c>
       <c r="F24" t="n">
-        <v>225.2141434809289</v>
+        <v>1.737954374179517</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3.431583156953879</v>
+        <v>5.689723622064391</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
         <v>4</v>
@@ -1417,28 +1417,28 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>258804.1613441213</v>
+        <v>258711.9734969056</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46052.22828717891</v>
+        <v>46052.84768206059</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46052.22981502196</v>
+        <v>46052.8489966245</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.001527843055555555</v>
+        <v>0.001314563912037037</v>
       </c>
       <c r="F25" t="n">
-        <v>155.2896620832054</v>
+        <v>3.260669108732458</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>18.86572292307279</v>
+        <v>2.637798891493488</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1457,34 +1457,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B26" t="n">
-        <v>258843.6627958062</v>
+        <v>258714.4148605861</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46051.9784571</v>
+        <v>46052.84390530557</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>46051.98000393101</v>
+        <v>46052.84524840161</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.001546831006944444</v>
+        <v>0.001343096041666667</v>
       </c>
       <c r="F26" t="n">
-        <v>66.40017753631193</v>
+        <v>70.5041701504708</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>505.0752973650522</v>
+        <v>35.70503066393538</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
@@ -1497,34 +1497,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B27" t="n">
-        <v>258892.8729323023</v>
+        <v>258771.0141945449</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46051.97196203412</v>
+        <v>46052.85207060938</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>46051.97374828895</v>
+        <v>46052.8531404137</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.001786254826388889</v>
+        <v>0.001069804328703704</v>
       </c>
       <c r="F27" t="n">
-        <v>12.25218287144648</v>
+        <v>35.4151581016398</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>670.8765666853044</v>
+        <v>3.145643870783142</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
@@ -1537,34 +1537,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>258918.9761555594</v>
+        <v>258813.534346935</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46051.97374828895</v>
+        <v>46052.84297833369</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>46051.97528076165</v>
+        <v>46052.84390530557</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.001532472696759259</v>
+        <v>0.0009269718749999999</v>
       </c>
       <c r="F28" t="n">
-        <v>32.77701570798548</v>
+        <v>2.276333448110351</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>447.8244658247332</v>
+        <v>9.249841185075876</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
@@ -1577,34 +1577,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>259337.1278573925</v>
+        <v>258815.4941990341</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46051.98165679038</v>
+        <v>46052.84524840161</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>46051.98293980383</v>
+        <v>46052.84645439409</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.001283013449074074</v>
+        <v>0.001205992476851852</v>
       </c>
       <c r="F29" t="n">
-        <v>415.7492248467317</v>
+        <v>6.372220597255474</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>648.3738781916479</v>
+        <v>1.700227652589913</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
@@ -1617,34 +1617,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B30" t="n">
-        <v>259345.6182053462</v>
+        <v>258849.0142788756</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46051.99177873067</v>
+        <v>46052.84645439409</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46051.99269935226</v>
+        <v>46052.84768204896</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.0009206215856481481</v>
+        <v>0.001227654872685185</v>
       </c>
       <c r="F30" t="n">
-        <v>4.63418601019545</v>
+        <v>6.533848222110998</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>81.43018020851031</v>
+        <v>7.610761326264606</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
@@ -1660,31 +1660,31 @@
         <v>0</v>
       </c>
       <c r="B31" t="n">
-        <v>259778.723540998</v>
+        <v>258895.1959425072</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46051.97075396999</v>
+        <v>46052.84208471324</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46051.97196202093</v>
+        <v>46052.84297831055</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0012080509375</v>
+        <v>0.0008935973032407407</v>
       </c>
       <c r="F31" t="n">
-        <v>156.1897170657543</v>
+        <v>19.16254630944987</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>701.8513239822224</v>
+        <v>27.14950950867848</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
         <v>4</v>
